--- a/zy72306/output/timeseries_anomaly.xlsx
+++ b/zy72306/output/timeseries_anomaly.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="异常分解结果" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工修改审计追踪" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="复核记录明细" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总统计" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,12 +504,67 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>review_records</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>updated_at</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>import_source</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>import_sheet_name</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>snapshot_version</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>manual_modifications_count</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>manual_modifications_json</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>review_records_count</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>review_records_json</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>latest_reviewed_by</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>latest_review_reason</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>latest_next_owner</t>
         </is>
       </c>
     </row>
@@ -532,7 +590,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>200</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -545,10 +603,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ProcessStatus.IMPORTED</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>ProcessStatus.FINALIZED</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>screenshot_001</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
@@ -559,14 +621,47 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275272</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275509</t>
-        </is>
-      </c>
+          <t>2026-06-09T01:11:20.518984</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:12:03.766059</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>sample_input.csv</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -585,9 +680,13 @@
       <c r="D3" t="n">
         <v>50</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>AnomalyType.NORMAL</t>
@@ -598,15 +697,19 @@
           <t>ProcessStatus.FINALIZED</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>screenshot_002</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>分母为空需复核，可能是数据录入错误</t>
+          <t>分母为空需复核，可能是数据录入错误，见旧公式截图 screenshot_002</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}, {'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}, {'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}, {'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}, {'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}, {'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}, {'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}, {'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}]</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -616,17 +719,62 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>确认分母应为100，录入时遗漏</t>
+          <t>按老师批注补填，标记normal</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275341</t>
+          <t>[{'reviewed_at': '2026-06-09T01:12:02.900225', 'reviewed_by': '数据复核人-张', 'original_statement': "公式截图中分母格为空，老师批注说'漏填了100'", 'corrected_value': '100', 'review_reason': '对比旧公式截图和老师批注，以老师批注为准，分母漏填', 'next_owner': '数据分析师小祁确认改后数', 'review_note': '按老师批注补填，标记normal', 'anomaly_type_after_review': &lt;AnomalyType.NORMAL: 'normal'&gt;}, {'reviewed_at': '2026-06-09T01:12:02.900225', 'reviewed_by': '数据复核人-张', 'original_statement': "公式截图中分母格为空，老师批注说'漏填了100'", 'corrected_value': '100', 'review_reason': '对比旧公式截图和老师批注，以老师批注为准，分母漏填', 'next_owner': '数据分析师小祁确认改后数', 'review_note': '按老师批注补填，标记normal', 'anomaly_type_after_review': &lt;AnomalyType.NORMAL: 'normal'&gt;}]</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275618</t>
+          <t>2026-06-09T01:11:20.518999</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:12:03.767445</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>sample_input.csv</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>[{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"},{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"},{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"},{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"},{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"},{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"},{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"},{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"}]</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>[{"reviewed_at":"2026-06-09T01:12:02.900225","reviewed_by":"数据复核人-张","original_statement":"公式截图中分母格为空，老师批注说'漏填了100'","corrected_value":"100","review_reason":"对比旧公式截图和老师批注，以老师批注为准，分母漏填","next_owner":"数据分析师小祁确认改后数","review_note":"按老师批注补填，标记normal","anomaly_type_after_review":"normal"},{"reviewed_at":"2026-06-09T01:12:02.900225","reviewed_by":"数据复核人-张","original_statement":"公式截图中分母格为空，老师批注说'漏填了100'","corrected_value":"100","review_reason":"对比旧公式截图和老师批注，以老师批注为准，分母漏填","next_owner":"数据分析师小祁确认改后数","review_note":"按老师批注补填，标记normal","anomaly_type_after_review":"normal"}]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>数据复核人-张</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>对比旧公式截图和老师批注，以老师批注为准，分母漏填</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>数据分析师小祁确认改后数</t>
         </is>
       </c>
     </row>
@@ -652,7 +800,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -666,10 +814,14 @@
           <t>ProcessStatus.FINALIZED</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>screenshot_003</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>分母为0但原始公式截图显示为空字符串</t>
+          <t>分母为0但原始公式截图显示为空字符串，和老师批注冲突，留待复核人</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -677,20 +829,69 @@
           <t>[]</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>BoundaryRuleType.ZERO_DENOMINATOR_EMPTY_STRING</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>分母为空字符串，按0处理，标记为异常</t>
+          <t>保持abnormal，用于课堂讲解</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275375</t>
+          <t>[{'reviewed_at': '2026-06-09T01:12:02.900237', 'reviewed_by': '数据复核人-张', 'original_statement': '分母原始显示为空字符串，数值是0', 'corrected_value': '0', 'review_reason': '空字符串就是0，按0处理，不提前归normal，按异常记', 'next_owner': '课堂演示环节重点说明', 'review_note': '保持abnormal，用于课堂讲解', 'anomaly_type_after_review': &lt;AnomalyType.ABNORMAL: 'abnormal'&gt;}, {'reviewed_at': '2026-06-09T01:12:02.900237', 'reviewed_by': '数据复核人-张', 'original_statement': '分母原始显示为空字符串，数值是0', 'corrected_value': '0', 'review_reason': '空字符串就是0，按0处理，不提前归normal，按异常记', 'next_owner': '课堂演示环节重点说明', 'review_note': '保持abnormal，用于课堂讲解', 'anomaly_type_after_review': &lt;AnomalyType.ABNORMAL: 'abnormal'&gt;}]</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275622</t>
+          <t>2026-06-09T01:11:20.519004</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:12:03.768430</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>sample_input.csv</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>2</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>[{"reviewed_at":"2026-06-09T01:12:02.900237","reviewed_by":"数据复核人-张","original_statement":"分母原始显示为空字符串，数值是0","corrected_value":"0","review_reason":"空字符串就是0，按0处理，不提前归normal，按异常记","next_owner":"课堂演示环节重点说明","review_note":"保持abnormal，用于课堂讲解","anomaly_type_after_review":"abnormal"},{"reviewed_at":"2026-06-09T01:12:02.900237","reviewed_by":"数据复核人-张","original_statement":"分母原始显示为空字符串，数值是0","corrected_value":"0","review_reason":"空字符串就是0，按0处理，不提前归normal，按异常记","next_owner":"课堂演示环节重点说明","review_note":"保持abnormal，用于课堂讲解","anomaly_type_after_review":"abnormal"}]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>数据复核人-张</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>空字符串就是0，按0处理，不提前归normal，按异常记</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>课堂演示环节重点说明</t>
         </is>
       </c>
     </row>
@@ -716,7 +917,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -729,10 +930,14 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ProcessStatus.IMPORTED</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>ProcessStatus.FINALIZED</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>screenshot_004</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
@@ -743,14 +948,47 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275404</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275522</t>
-        </is>
-      </c>
+          <t>2026-06-09T01:11:20.519008</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:12:03.769374</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>sample_input.csv</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -774,7 +1012,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>400.0</t>
+          <t>400</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -787,10 +1025,14 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ProcessStatus.IMPORTED</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>ProcessStatus.FINALIZED</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>screenshot_005</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
@@ -805,14 +1047,47 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275428</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275526</t>
-        </is>
-      </c>
+          <t>2026-06-09T01:11:20.519011</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:12:03.770330</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>sample_input.csv</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -836,18 +1111,22 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AnomalyType.BOUNDARY_CASE</t>
+          <t>AnomalyType.PENDING_VERIFICATION</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ProcessStatus.FINALIZED</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>ProcessStatus.REVIEWED</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>screenshot_006</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>空值记录，待与数据源方确认</t>
+          <t>空值记录，待与数据源方确认是否该补为100</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -862,17 +1141,62 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>数据缺失，无法计算，保留边界案例标记</t>
+          <t>继续pending_verification，不finalize</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275450</t>
+          <t>[{'reviewed_at': '2026-06-09T01:12:02.900239', 'reviewed_by': '数据复核人-张', 'original_statement': "旧截图中该行为空，老师批注'数据源方确认'", 'corrected_value': '', 'review_reason': '数据源方还没回复，继续挂待验证，不提前归normal', 'next_owner': '下周找数据源方追数', 'review_note': '继续pending_verification，不finalize', 'anomaly_type_after_review': &lt;AnomalyType.PENDING_VERIFICATION: 'pending_verification'&gt;}]</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275626</t>
+          <t>2026-06-09T01:11:20.519014</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:12:02.902062</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>sample_input.csv</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>[{"reviewed_at":"2026-06-09T01:12:02.900239","reviewed_by":"数据复核人-张","original_statement":"旧截图中该行为空，老师批注'数据源方确认'","corrected_value":"","review_reason":"数据源方还没回复，继续挂待验证，不提前归normal","next_owner":"下周找数据源方追数","review_note":"继续pending_verification，不finalize","anomaly_type_after_review":"pending_verification"}]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>数据复核人-张</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>数据源方还没回复，继续挂待验证，不提前归normal</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>下周找数据源方追数</t>
         </is>
       </c>
     </row>
@@ -898,7 +1222,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>180</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -911,10 +1235,14 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ProcessStatus.IMPORTED</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>ProcessStatus.FINALIZED</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>screenshot_007</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
@@ -925,14 +1253,47 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275472</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275533</t>
-        </is>
-      </c>
+          <t>2026-06-09T01:11:20.519017</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:12:03.771955</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>sample_input.csv</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -956,7 +1317,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -969,10 +1330,14 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ProcessStatus.IMPORTED</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>ProcessStatus.FINALIZED</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>screenshot_008</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
@@ -987,13 +1352,880 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275494</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-04T06:35:12.275536</t>
-        </is>
+          <t>2026-06-09T01:11:20.519020</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:12:03.773328</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>sample_input.csv</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>行号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>指标名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>修改时间</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>修改人</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>修改字段</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>原值</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>新值</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>修改原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>转化率B</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:11:21.764361</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>数据分析师小祁</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>denominator</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>转化率B</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:11:21.764361</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>数据分析师小祁</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>denominator</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>转化率B</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:11:21.764361</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>数据分析师小祁</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>denominator</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>转化率B</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:11:21.764361</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>数据分析师小祁</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>denominator</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>转化率B</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:11:21.764361</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>数据分析师小祁</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>denominator</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>转化率B</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:11:21.764361</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>数据分析师小祁</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>denominator</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>转化率B</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:11:21.764361</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>数据分析师小祁</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>denominator</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>转化率B</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:11:21.764361</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>数据分析师小祁</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>denominator</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>行号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>指标名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>原始分母值</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>复核时间</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>复核人</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>原始说法</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>改后的值</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>处理原因</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>下一步找谁</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>复核备注</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>复核后异常类型</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>转化率B</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:12:02.900225</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>数据复核人-张</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>公式截图中分母格为空，老师批注说'漏填了100'</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>对比旧公式截图和老师批注，以老师批注为准，分母漏填</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>数据分析师小祁确认改后数</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>按老师批注补填，标记normal</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>转化率B</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:12:02.900225</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>数据复核人-张</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>公式截图中分母格为空，老师批注说'漏填了100'</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>对比旧公式截图和老师批注，以老师批注为准，分母漏填</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>数据分析师小祁确认改后数</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>按老师批注补填，标记normal</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>转化率C</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:12:02.900237</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>数据复核人-张</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>分母原始显示为空字符串，数值是0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>空字符串就是0，按0处理，不提前归normal，按异常记</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>课堂演示环节重点说明</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>保持abnormal，用于课堂讲解</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>abnormal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>转化率C</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:12:02.900237</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>数据复核人-张</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>分母原始显示为空字符串，数值是0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>空字符串就是0，按0处理，不提前归normal，按异常记</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>课堂演示环节重点说明</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>保持abnormal，用于课堂讲解</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>abnormal</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>转化率C</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-06-09T01:12:02.900239</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>数据复核人-张</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>旧截图中该行为空，老师批注'数据源方确认'</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>数据源方还没回复，继续挂待验证，不提前归normal</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>下周找数据源方追数</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>继续pending_verification，不finalize</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>pending_verification</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>指标</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>记录总数</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>待验证（分母0空字符串）</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>待复核</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>已最终确认</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>人工修改次数</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>复核记录数</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>异常类型</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>abnormal</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>pending_verification</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/zy72306/output/timeseries_anomaly.xlsx
+++ b/zy72306/output/timeseries_anomaly.xlsx
@@ -9,8 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="异常分解结果" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="人工修改审计追踪" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="复核记录明细" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总统计" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="汇总统计" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -603,7 +602,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ProcessStatus.FINALIZED</t>
+          <t>ProcessStatus.IMPORTED</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -626,12 +625,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-06-09T01:11:20.518984</t>
+          <t>2026-06-19T14:59:53.565259</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-06-09T01:12:03.766059</t>
+          <t>2026-06-19T14:59:53.565301</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -641,7 +640,7 @@
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -689,12 +688,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AnomalyType.NORMAL</t>
+          <t>AnomalyType.PENDING_VERIFICATION</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ProcessStatus.FINALIZED</t>
+          <t>ProcessStatus.MANUAL_UPDATED</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -702,14 +701,10 @@
           <t>screenshot_002</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>分母为空需复核，可能是数据录入错误，见旧公式截图 screenshot_002</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>[{'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}, {'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}, {'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}, {'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}, {'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}, {'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}, {'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}, {'modified_at': '2026-06-09T01:11:21.764361', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '根据旧公式截图 screenshot_002 老师批注漏填了100补录'}]</t>
+          <t>[{'modified_at': '2026-06-19T14:59:54.146119', 'modified_by': '数据分析师小祁', 'field_name': 'denominator', 'old_value': 'None', 'new_value': '100', 'reason': '测试API同步'}]</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -717,24 +712,20 @@
           <t>BoundaryRuleType.ZERO_DENOMINATOR_EMPTY_STRING</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>按老师批注补填，标记normal</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>[{'reviewed_at': '2026-06-09T01:12:02.900225', 'reviewed_by': '数据复核人-张', 'original_statement': "公式截图中分母格为空，老师批注说'漏填了100'", 'corrected_value': '100', 'review_reason': '对比旧公式截图和老师批注，以老师批注为准，分母漏填', 'next_owner': '数据分析师小祁确认改后数', 'review_note': '按老师批注补填，标记normal', 'anomaly_type_after_review': &lt;AnomalyType.NORMAL: 'normal'&gt;}, {'reviewed_at': '2026-06-09T01:12:02.900225', 'reviewed_by': '数据复核人-张', 'original_statement': "公式截图中分母格为空，老师批注说'漏填了100'", 'corrected_value': '100', 'review_reason': '对比旧公式截图和老师批注，以老师批注为准，分母漏填', 'next_owner': '数据分析师小祁确认改后数', 'review_note': '按老师批注补填，标记normal', 'anomaly_type_after_review': &lt;AnomalyType.NORMAL: 'normal'&gt;}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-06-09T01:11:20.518999</t>
+          <t>2026-06-19T14:59:53.565264</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-06-09T01:12:03.767445</t>
+          <t>2026-06-19T14:59:54.146158</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -744,39 +735,27 @@
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>[{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"},{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"},{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"},{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"},{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"},{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"},{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"},{"modified_at":"2026-06-09T01:11:21.764361","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"根据旧公式截图 screenshot_002 老师批注漏填了100补录"}]</t>
+          <t>[{"modified_at":"2026-06-19T14:59:54.146119","modified_by":"数据分析师小祁","field_name":"denominator","old_value":"None","new_value":"100","reason":"测试API同步"}]</t>
         </is>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>[{"reviewed_at":"2026-06-09T01:12:02.900225","reviewed_by":"数据复核人-张","original_statement":"公式截图中分母格为空，老师批注说'漏填了100'","corrected_value":"100","review_reason":"对比旧公式截图和老师批注，以老师批注为准，分母漏填","next_owner":"数据分析师小祁确认改后数","review_note":"按老师批注补填，标记normal","anomaly_type_after_review":"normal"},{"reviewed_at":"2026-06-09T01:12:02.900225","reviewed_by":"数据复核人-张","original_statement":"公式截图中分母格为空，老师批注说'漏填了100'","corrected_value":"100","review_reason":"对比旧公式截图和老师批注，以老师批注为准，分母漏填","next_owner":"数据分析师小祁确认改后数","review_note":"按老师批注补填，标记normal","anomaly_type_after_review":"normal"}]</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>数据复核人-张</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>对比旧公式截图和老师批注，以老师批注为准，分母漏填</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>数据分析师小祁确认改后数</t>
-        </is>
-      </c>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -806,12 +785,12 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AnomalyType.ABNORMAL</t>
+          <t>AnomalyType.PENDING_VERIFICATION</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ProcessStatus.FINALIZED</t>
+          <t>ProcessStatus.IMPORTED</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -819,11 +798,7 @@
           <t>screenshot_003</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>分母为0但原始公式截图显示为空字符串，和老师批注冲突，留待复核人</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -834,24 +809,20 @@
           <t>BoundaryRuleType.ZERO_DENOMINATOR_EMPTY_STRING</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>保持abnormal，用于课堂讲解</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>[{'reviewed_at': '2026-06-09T01:12:02.900237', 'reviewed_by': '数据复核人-张', 'original_statement': '分母原始显示为空字符串，数值是0', 'corrected_value': '0', 'review_reason': '空字符串就是0，按0处理，不提前归normal，按异常记', 'next_owner': '课堂演示环节重点说明', 'review_note': '保持abnormal，用于课堂讲解', 'anomaly_type_after_review': &lt;AnomalyType.ABNORMAL: 'abnormal'&gt;}, {'reviewed_at': '2026-06-09T01:12:02.900237', 'reviewed_by': '数据复核人-张', 'original_statement': '分母原始显示为空字符串，数值是0', 'corrected_value': '0', 'review_reason': '空字符串就是0，按0处理，不提前归normal，按异常记', 'next_owner': '课堂演示环节重点说明', 'review_note': '保持abnormal，用于课堂讲解', 'anomaly_type_after_review': &lt;AnomalyType.ABNORMAL: 'abnormal'&gt;}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-06-09T01:11:20.519004</t>
+          <t>2026-06-19T14:59:53.565267</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-06-09T01:12:03.768430</t>
+          <t>2026-06-19T14:59:53.565304</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -861,7 +832,7 @@
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -872,28 +843,16 @@
         </is>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>[{"reviewed_at":"2026-06-09T01:12:02.900237","reviewed_by":"数据复核人-张","original_statement":"分母原始显示为空字符串，数值是0","corrected_value":"0","review_reason":"空字符串就是0，按0处理，不提前归normal，按异常记","next_owner":"课堂演示环节重点说明","review_note":"保持abnormal，用于课堂讲解","anomaly_type_after_review":"abnormal"},{"reviewed_at":"2026-06-09T01:12:02.900237","reviewed_by":"数据复核人-张","original_statement":"分母原始显示为空字符串，数值是0","corrected_value":"0","review_reason":"空字符串就是0，按0处理，不提前归normal，按异常记","next_owner":"课堂演示环节重点说明","review_note":"保持abnormal，用于课堂讲解","anomaly_type_after_review":"abnormal"}]</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>数据复核人-张</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>空字符串就是0，按0处理，不提前归normal，按异常记</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>课堂演示环节重点说明</t>
-        </is>
-      </c>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -930,7 +889,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ProcessStatus.FINALIZED</t>
+          <t>ProcessStatus.IMPORTED</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -953,12 +912,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-06-09T01:11:20.519008</t>
+          <t>2026-06-19T14:59:53.565270</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-06-09T01:12:03.769374</t>
+          <t>2026-06-19T14:59:53.565304</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -968,7 +927,7 @@
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1025,7 +984,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ProcessStatus.FINALIZED</t>
+          <t>ProcessStatus.IMPORTED</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1052,12 +1011,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-06-09T01:11:20.519011</t>
+          <t>2026-06-19T14:59:53.565273</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-06-09T01:12:03.770330</t>
+          <t>2026-06-19T14:59:53.565305</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1067,7 +1026,7 @@
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1116,7 +1075,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ProcessStatus.REVIEWED</t>
+          <t>ProcessStatus.IMPORTED</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1124,11 +1083,7 @@
           <t>screenshot_006</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>空值记录，待与数据源方确认是否该补为100</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1139,24 +1094,20 @@
           <t>BoundaryRuleType.ZERO_DENOMINATOR_EMPTY_STRING</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>继续pending_verification，不finalize</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>[{'reviewed_at': '2026-06-09T01:12:02.900239', 'reviewed_by': '数据复核人-张', 'original_statement': "旧截图中该行为空，老师批注'数据源方确认'", 'corrected_value': '', 'review_reason': '数据源方还没回复，继续挂待验证，不提前归normal', 'next_owner': '下周找数据源方追数', 'review_note': '继续pending_verification，不finalize', 'anomaly_type_after_review': &lt;AnomalyType.PENDING_VERIFICATION: 'pending_verification'&gt;}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-06-09T01:11:20.519014</t>
+          <t>2026-06-19T14:59:53.565276</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-06-09T01:12:02.902062</t>
+          <t>2026-06-19T14:59:53.565306</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1166,7 +1117,7 @@
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1177,28 +1128,16 @@
         </is>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>[{"reviewed_at":"2026-06-09T01:12:02.900239","reviewed_by":"数据复核人-张","original_statement":"旧截图中该行为空，老师批注'数据源方确认'","corrected_value":"","review_reason":"数据源方还没回复，继续挂待验证，不提前归normal","next_owner":"下周找数据源方追数","review_note":"继续pending_verification，不finalize","anomaly_type_after_review":"pending_verification"}]</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>数据复核人-张</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>数据源方还没回复，继续挂待验证，不提前归normal</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>下周找数据源方追数</t>
-        </is>
-      </c>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1235,7 +1174,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ProcessStatus.FINALIZED</t>
+          <t>ProcessStatus.IMPORTED</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1258,12 +1197,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-06-09T01:11:20.519017</t>
+          <t>2026-06-19T14:59:53.565278</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-06-09T01:12:03.771955</t>
+          <t>2026-06-19T14:59:53.565306</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1273,7 +1212,7 @@
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1330,7 +1269,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ProcessStatus.FINALIZED</t>
+          <t>ProcessStatus.IMPORTED</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1357,12 +1296,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-06-09T01:11:20.519020</t>
+          <t>2026-06-19T14:59:53.565281</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-06-09T01:12:03.773328</t>
+          <t>2026-06-19T14:59:53.565307</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1372,7 +1311,7 @@
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1405,7 +1344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1461,7 +1400,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-06-09T01:11:21.764361</t>
+          <t>2026-06-19T14:59:54.146119</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1486,287 +1425,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>转化率B</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-06-09T01:11:21.764361</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>数据分析师小祁</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>denominator</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>转化率B</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-06-09T01:11:21.764361</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>数据分析师小祁</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>denominator</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>转化率B</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-06-09T01:11:21.764361</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>数据分析师小祁</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>denominator</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>转化率B</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-06-09T01:11:21.764361</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>数据分析师小祁</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>denominator</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>转化率B</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-06-09T01:11:21.764361</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>数据分析师小祁</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>denominator</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>转化率B</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-06-09T01:11:21.764361</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>数据分析师小祁</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>denominator</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>转化率B</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-06-09T01:11:21.764361</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>数据分析师小祁</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>denominator</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>根据旧公式截图 screenshot_002 老师批注漏填了100补录</t>
+          <t>测试API同步</t>
         </is>
       </c>
     </row>
@@ -1781,336 +1440,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>行号</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>指标名称</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>原始分母值</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>复核时间</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>复核人</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>原始说法</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>改后的值</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>处理原因</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>下一步找谁</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>复核备注</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>复核后异常类型</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>转化率B</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-06-09T01:12:02.900225</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>数据复核人-张</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>公式截图中分母格为空，老师批注说'漏填了100'</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>对比旧公式截图和老师批注，以老师批注为准，分母漏填</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>数据分析师小祁确认改后数</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>按老师批注补填，标记normal</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>转化率B</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-06-09T01:12:02.900225</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>数据复核人-张</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>公式截图中分母格为空，老师批注说'漏填了100'</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>对比旧公式截图和老师批注，以老师批注为准，分母漏填</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>数据分析师小祁确认改后数</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>按老师批注补填，标记normal</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>转化率C</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-06-09T01:12:02.900237</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>数据复核人-张</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>分母原始显示为空字符串，数值是0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>空字符串就是0，按0处理，不提前归normal，按异常记</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>课堂演示环节重点说明</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>保持abnormal，用于课堂讲解</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>abnormal</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>转化率C</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-06-09T01:12:02.900237</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>数据复核人-张</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>分母原始显示为空字符串，数值是0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>空字符串就是0，按0处理，不提前归normal，按异常记</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>课堂演示环节重点说明</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>保持abnormal，用于课堂讲解</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>abnormal</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>转化率C</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-06-09T01:12:02.900239</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>数据复核人-张</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>旧截图中该行为空，老师批注'数据源方确认'</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>数据源方还没回复，继续挂待验证，不提前归normal</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>下周找数据源方追数</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>继续pending_verification，不finalize</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>pending_verification</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -2143,7 +1472,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2163,7 +1492,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -2173,7 +1502,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2183,7 +1512,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2205,13 +1534,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>abnormal</t>
+          <t>pending_verification</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2221,11 +1550,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>pending_verification</t>
+          <t>abnormal</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
